--- a/data/s2/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s2/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s2\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E31350-A598-42E9-A30B-70984A1367A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FF7287-B6E2-44D0-9304-DA9ADC37D225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2136" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M3" s="2">
         <v>62.984000000000002</v>
@@ -873,7 +873,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="L4" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -955,7 +955,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="L5" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M5" s="2">
         <v>53.112000000000002</v>
@@ -1035,7 +1035,7 @@
         <v>0.05</v>
       </c>
       <c r="L6" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M6" s="2">
         <v>43.322000000000003</v>
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M7" s="7">
         <f>293.323/30</f>
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M9" s="7">
         <f>357.554/30</f>
@@ -1370,8 +1370,8 @@
       <c r="K10">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" s="2">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M10" s="2">
         <v>0</v>
@@ -1422,7 +1422,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A10:L10 A11:XFD1048576">
+  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A10:K10 A11:XFD1048576">
     <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
       <formula>0</formula>
     </cfRule>

--- a/data/s2/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s2/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s2\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FF7287-B6E2-44D0-9304-DA9ADC37D225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A202A2D-E242-41D7-9041-627A16D85E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -169,27 +169,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -204,13 +187,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,85 +210,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -592,7 +505,7 @@
     <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="7.88671875" customWidth="1"/>
     <col min="13" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="11.109375" style="5" customWidth="1"/>
+    <col min="17" max="18" width="11.109375" customWidth="1"/>
     <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -604,83 +517,83 @@
     <col min="28" max="29" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -709,10 +622,10 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="12">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
@@ -721,28 +634,28 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2" s="11">
-        <v>0</v>
-      </c>
-      <c r="P2" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="8">
-        <v>0</v>
-      </c>
-      <c r="T2" s="8">
-        <v>0</v>
-      </c>
-      <c r="U2" s="14">
-        <v>0</v>
-      </c>
-      <c r="V2" s="14">
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
         <v>0</v>
       </c>
       <c r="W2">
@@ -777,10 +690,10 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
       <c r="I3">
@@ -789,41 +702,41 @@
       <c r="J3">
         <v>0.1</v>
       </c>
-      <c r="K3" s="12">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="L3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>62.984000000000002</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>2.94</v>
       </c>
-      <c r="O3" s="12">
-        <v>2.6709999999999998</v>
-      </c>
-      <c r="P3" s="12">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="Q3" s="6">
+      <c r="O3" s="1">
+        <v>2.6535000000000002</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="Q3" s="1">
         <v>9999</v>
       </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="14">
-        <v>131.40600000000001</v>
-      </c>
-      <c r="V3" s="14">
-        <v>47.3</v>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>177.6465</v>
+      </c>
+      <c r="V3" s="1">
+        <v>13.9895</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -857,10 +770,10 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
       <c r="I4">
@@ -869,10 +782,10 @@
       <c r="J4">
         <v>0.1</v>
       </c>
-      <c r="K4" s="12">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="K4" s="1">
+        <v>0.10075000000000001</v>
+      </c>
+      <c r="L4">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
@@ -881,30 +794,30 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="12">
-        <v>0.63349999999999995</v>
-      </c>
-      <c r="P4" s="12">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q4" s="6">
+      <c r="O4" s="1">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="P4" s="1">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="Q4" s="1">
         <v>9999</v>
       </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9">
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <f>O4*0.5</f>
-        <v>0.31674999999999998</v>
-      </c>
-      <c r="T4" s="9">
+        <v>0.41649999999999998</v>
+      </c>
+      <c r="T4">
         <f>P4*0.5</f>
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="U4" s="14">
-        <v>0</v>
-      </c>
-      <c r="V4" s="14">
+        <v>2.375E-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
         <v>0</v>
       </c>
       <c r="W4">
@@ -939,10 +852,10 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
       <c r="I5">
@@ -951,41 +864,41 @@
       <c r="J5">
         <v>0.1</v>
       </c>
-      <c r="K5" s="12">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="K5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="L5">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>53.112000000000002</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>3.9049999999999998</v>
       </c>
-      <c r="O5" s="12">
-        <v>1.6359999999999999</v>
-      </c>
-      <c r="P5" s="12">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="Q5" s="6">
+      <c r="O5" s="1">
+        <v>2.2280000000000002</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.16850000000000001</v>
+      </c>
+      <c r="Q5" s="1">
         <v>9999</v>
       </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8">
-        <v>0</v>
-      </c>
-      <c r="U5" s="14">
-        <v>111.25</v>
-      </c>
-      <c r="V5" s="14">
-        <v>47.622</v>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>150.09649999999999</v>
+      </c>
+      <c r="V5" s="1">
+        <v>20.7745</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1019,10 +932,10 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6">
@@ -1031,41 +944,41 @@
       <c r="J6">
         <v>0.1</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6">
         <v>0.05</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>43.322000000000003</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>2.206</v>
       </c>
-      <c r="O6" s="12">
-        <v>1.9750000000000001</v>
-      </c>
-      <c r="P6" s="12">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="O6" s="1">
+        <v>2.032</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.2175</v>
+      </c>
+      <c r="Q6" s="1">
         <v>9999</v>
       </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
-        <v>0</v>
-      </c>
-      <c r="U6" s="14">
-        <v>27.818000000000001</v>
-      </c>
-      <c r="V6" s="14">
-        <v>50.091000000000001</v>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>41.872</v>
+      </c>
+      <c r="V6" s="1">
+        <v>60.761499999999998</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1099,10 +1012,10 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="I7">
@@ -1111,47 +1024,48 @@
       <c r="J7">
         <v>0.1</v>
       </c>
-      <c r="K7" s="12">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7" s="1">
+        <f>4/21*0.5</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="L7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7">
         <f>293.323/30</f>
         <v>9.7774333333333328</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7">
         <f>38.284/30</f>
         <v>1.2761333333333333</v>
       </c>
-      <c r="O7" s="13">
-        <f>8.911/30</f>
-        <v>0.29703333333333332</v>
-      </c>
-      <c r="P7" s="13">
-        <f>3.4925/30</f>
-        <v>0.11641666666666667</v>
-      </c>
-      <c r="Q7" s="6">
+      <c r="O7" s="2">
+        <f>13.1245/45</f>
+        <v>0.29165555555555556</v>
+      </c>
+      <c r="P7" s="2">
+        <f>1.7305/45</f>
+        <v>3.8455555555555555E-2</v>
+      </c>
+      <c r="Q7" s="1">
         <v>9999</v>
       </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="14">
-        <f>525.4055/30</f>
-        <v>17.513516666666664</v>
-      </c>
-      <c r="V7" s="14">
-        <f>306.889/30</f>
-        <v>10.229633333333334</v>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <f>788.65/45</f>
+        <v>17.525555555555556</v>
+      </c>
+      <c r="V7" s="2">
+        <f>283.759/45</f>
+        <v>6.3057555555555558</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1185,10 +1099,10 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>37</v>
       </c>
       <c r="I8">
@@ -1197,10 +1111,11 @@
       <c r="J8">
         <v>0.1</v>
       </c>
-      <c r="K8" s="12">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="K8" s="1">
+        <f t="shared" ref="K8:K9" si="0">4/21*0.5</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="L8">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
@@ -1209,32 +1124,32 @@
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8" s="12">
-        <f>4.2125/30</f>
-        <v>0.14041666666666669</v>
-      </c>
-      <c r="P8" s="12">
-        <f>2.223/30</f>
-        <v>7.4099999999999999E-2</v>
-      </c>
-      <c r="Q8" s="6">
+      <c r="O8" s="2">
+        <f>5.5995/45</f>
+        <v>0.12443333333333333</v>
+      </c>
+      <c r="P8" s="2">
+        <f>1.663/45</f>
+        <v>3.6955555555555554E-2</v>
+      </c>
+      <c r="Q8" s="1">
         <v>9999</v>
       </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9">
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <f>O8*0.5</f>
-        <v>7.0208333333333345E-2</v>
-      </c>
-      <c r="T8" s="9">
+        <v>6.2216666666666663E-2</v>
+      </c>
+      <c r="T8">
         <f>P8*0.5</f>
-        <v>3.705E-2</v>
-      </c>
-      <c r="U8" s="14">
-        <v>0</v>
-      </c>
-      <c r="V8" s="14">
+        <v>1.8477777777777777E-2</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
         <v>0</v>
       </c>
       <c r="W8">
@@ -1269,10 +1184,10 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
       <c r="I9">
@@ -1281,47 +1196,44 @@
       <c r="J9">
         <v>0.1</v>
       </c>
-      <c r="K9" s="12">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="L9">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <f>357.554/30</f>
         <v>11.918466666666665</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <f>68.396/30</f>
         <v>2.2798666666666665</v>
       </c>
-      <c r="O9" s="13">
-        <f>12.258/30</f>
-        <v>0.40859999999999996</v>
-      </c>
-      <c r="P9" s="13">
-        <f>5.555/30</f>
-        <v>0.18516666666666665</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="O9" s="1">
+        <v>16.536999999999999</v>
+      </c>
+      <c r="P9" s="1">
+        <v>2.5804999999999998</v>
+      </c>
+      <c r="Q9" s="1">
         <v>9999</v>
       </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="14">
-        <f>257.1525/30</f>
-        <v>8.5717499999999998</v>
-      </c>
-      <c r="V9" s="14">
-        <f>364.766/30</f>
-        <v>12.158866666666666</v>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>441.87099999999998</v>
+      </c>
+      <c r="V9" s="1">
+        <v>381.6705</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1367,28 +1279,28 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10" s="1">
+        <v>0.10075000000000001</v>
+      </c>
+      <c r="L10">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="P10" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q10" s="6">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="P10" s="1">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="Q10" s="1">
         <v>9999</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="1">
         <v>0</v>
       </c>
       <c r="S10">
@@ -1397,10 +1309,10 @@
       <c r="T10">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
         <v>0</v>
       </c>
       <c r="W10">
@@ -1417,51 +1329,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:J9">
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A10:K10 A11:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4:P4">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:P8">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:XFD3">
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:R10">
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S7">
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S8:T10">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:XFD10">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/s2/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s2/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s2\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A202A2D-E242-41D7-9041-627A16D85E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDAA391-98B6-40D7-A134-0EED5D6B3DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +197,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -210,10 +216,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1279,8 +1286,8 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10" s="1">
-        <v>0.10075000000000001</v>
+      <c r="K10" s="3">
+        <v>0.60912938331318023</v>
       </c>
       <c r="L10">
         <v>1.0000000000000001E-5</v>
